--- a/Pedido.xlsx
+++ b/Pedido.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EB5B89-358A-45AE-BA60-DB18A8C2A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CA4CAC-CB44-43E0-92F2-AD526AB7151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{47FFAFD5-2359-4686-87DF-862FB9FF7A6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="158">
   <si>
     <t>Maizena</t>
   </si>
@@ -925,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14E6BC3-F9AC-40AB-81B2-1CF8A5CF62C6}">
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.90625" customWidth="1"/>
@@ -1365,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>44</v>
@@ -1376,7 +1376,7 @@
         <v>48</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>44</v>
@@ -1387,7 +1387,7 @@
         <v>49</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>44</v>
@@ -1398,7 +1398,7 @@
         <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>44</v>
@@ -1409,7 +1409,7 @@
         <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>44</v>
@@ -1420,7 +1420,7 @@
         <v>52</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>44</v>
@@ -1431,7 +1431,7 @@
         <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>44</v>
@@ -1442,7 +1442,7 @@
         <v>54</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>44</v>
@@ -1453,7 +1453,7 @@
         <v>55</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>44</v>
@@ -1464,7 +1464,7 @@
         <v>57</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>44</v>
@@ -1475,7 +1475,7 @@
         <v>58</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>44</v>
@@ -1486,7 +1486,7 @@
         <v>59</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>44</v>
@@ -1497,7 +1497,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>44</v>
@@ -1508,7 +1508,7 @@
         <v>61</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>44</v>
@@ -1519,7 +1519,7 @@
         <v>62</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>44</v>
@@ -1530,7 +1530,7 @@
         <v>63</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>44</v>
@@ -1541,7 +1541,7 @@
         <v>64</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>44</v>
@@ -1552,7 +1552,7 @@
         <v>65</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>44</v>
@@ -1563,7 +1563,7 @@
         <v>66</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>44</v>
@@ -1574,7 +1574,7 @@
         <v>67</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>44</v>
@@ -1585,7 +1585,7 @@
         <v>68</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>44</v>
@@ -1596,7 +1596,7 @@
         <v>69</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>44</v>
@@ -1607,7 +1607,7 @@
         <v>70</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>44</v>
@@ -1618,7 +1618,7 @@
         <v>71</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>44</v>
@@ -1629,7 +1629,7 @@
         <v>72</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>44</v>
@@ -1640,7 +1640,7 @@
         <v>73</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>44</v>
@@ -1650,8 +1650,8 @@
       <c r="A66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>56</v>
+      <c r="B66" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>44</v>
@@ -1661,8 +1661,8 @@
       <c r="A67" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>56</v>
+      <c r="B67" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>44</v>
@@ -1673,7 +1673,7 @@
         <v>76</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>44</v>
@@ -1684,7 +1684,7 @@
         <v>77</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>44</v>
@@ -1695,7 +1695,7 @@
         <v>79</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>44</v>
@@ -1706,7 +1706,7 @@
         <v>80</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>44</v>
@@ -1717,7 +1717,7 @@
         <v>81</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>44</v>
@@ -1728,7 +1728,7 @@
         <v>82</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>44</v>
@@ -1739,7 +1739,7 @@
         <v>83</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>44</v>
@@ -1750,7 +1750,7 @@
         <v>84</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>44</v>
@@ -1761,7 +1761,7 @@
         <v>85</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>44</v>
@@ -1772,7 +1772,7 @@
         <v>86</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>44</v>
@@ -1783,7 +1783,7 @@
         <v>87</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>44</v>
@@ -1794,7 +1794,7 @@
         <v>88</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>44</v>
@@ -1805,7 +1805,7 @@
         <v>89</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>44</v>
@@ -1816,7 +1816,7 @@
         <v>90</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>44</v>
@@ -1827,7 +1827,7 @@
         <v>91</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>44</v>
@@ -1838,7 +1838,7 @@
         <v>92</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>44</v>
@@ -1849,7 +1849,7 @@
         <v>93</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>44</v>
@@ -1860,7 +1860,7 @@
         <v>94</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>44</v>
@@ -1871,7 +1871,7 @@
         <v>95</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>44</v>
@@ -1882,7 +1882,7 @@
         <v>96</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>44</v>
@@ -1893,7 +1893,7 @@
         <v>97</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>44</v>
@@ -1904,7 +1904,7 @@
         <v>98</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>44</v>
@@ -1915,7 +1915,7 @@
         <v>99</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>44</v>
@@ -1926,7 +1926,7 @@
         <v>100</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>44</v>
@@ -1937,7 +1937,7 @@
         <v>101</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>44</v>
@@ -1948,7 +1948,7 @@
         <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>44</v>
@@ -1959,7 +1959,7 @@
         <v>103</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>44</v>
@@ -1969,8 +1969,8 @@
       <c r="A95" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>78</v>
+      <c r="B95" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>44</v>
@@ -2000,7 +2000,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>78</v>
@@ -2011,18 +2011,18 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>1</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>1</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>1</v>
@@ -2055,18 +2055,18 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B103" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>1</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>1</v>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>1</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>1</v>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>1</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>1</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>1</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>1</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>1</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>1</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>1</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>1</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>1</v>
@@ -2220,9 +2220,9 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B118" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C118" s="1" t="s">
@@ -2231,7 +2231,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>1</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>1</v>
@@ -2253,7 +2253,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>1</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>1</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>1</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>1</v>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>114</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>33</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>33</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>33</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>33</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>33</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>33</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>33</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>114</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>40</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>40</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>40</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>114</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>150</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>150</v>
@@ -2473,23 +2473,12 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C142" s="1" t="s">
         <v>154</v>
       </c>
     </row>
